--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7088.36</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057402-6695-CM26</t>
+          <t>1057402-6694-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4027.91</v>
+        <v>2528.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057402-6694-CM26</t>
+          <t>1057402-6588-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2520.92</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="9">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4426.15</v>
+        <v>4439.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057402-6588-CM26</t>
+          <t>1057402-6695-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3847.83</v>
+        <v>4040.37</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3962.63</v>
+        <v>3974.88</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4339.83</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8367.860000000001</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4339.83</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5720.37</v>
+        <v>5691.39</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3733.82</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="20">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5866.27</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>1057402-7245-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3733.82</v>
+        <v>4273.24</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6446.79</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="23">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7289.48</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057402-7245-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4295</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4295</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6343.69</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3733.82</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4211.23</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,190 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3908.56</v>
+        <v>3900.73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1057402-7871-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>6470.64</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1057402-8279-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>3934.26</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1057402-8542-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>3980.3</v>
       </c>
     </row>
   </sheetData>
